--- a/output/pdf_financials_xlsx/VRTS.xlsx
+++ b/output/pdf_financials_xlsx/VRTS.xlsx
@@ -5400,30 +5400,28 @@
         <v>0.037599</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0.059706</v>
-      </c>
-      <c r="F92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.064526</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.068089</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.068089</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.068089</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.068089</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.068089</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.804722</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.517444</v>
       </c>
       <c r="M92" s="1" t="inlineStr">
         <is>
@@ -5431,10 +5429,10 @@
         </is>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.619338</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.614338</v>
       </c>
     </row>
     <row r="93">
@@ -10278,7 +10276,11 @@
           <t>Warrant reserve 14</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -12448,7 +12450,11 @@
           <t>Warrant reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -13320,7 +13326,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14718,7 +14728,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -15822,7 +15836,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VRTS.xlsx
+++ b/output/pdf_financials_xlsx/VRTS.xlsx
@@ -2205,16 +2205,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.232843</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.104644</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.151331</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.023922</v>
       </c>
       <c r="F34" s="1" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000813</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.752581</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.556804</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.50613</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.171619</v>
       </c>
     </row>
     <row r="35">
@@ -2311,16 +2311,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.232843</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.104644</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.151331</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.023922</v>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.000813</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.752581</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.556804</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -2351,10 +2351,10 @@
         </is>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.50613</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.171619</v>
       </c>
     </row>
     <row r="37">
@@ -2943,16 +2943,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.263711</v>
+        <v>0.030868</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.158808</v>
+        <v>0.054164</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.170084</v>
+        <v>0.018753</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.036949</v>
+        <v>0.013027</v>
       </c>
       <c r="F48" s="1" t="inlineStr">
         <is>
@@ -2972,10 +2972,10 @@
         <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>4.056009</v>
+        <v>0.303428</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.709346</v>
+        <v>0.152542</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -2983,10 +2983,10 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.70909</v>
+        <v>0.20296</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.387673</v>
+        <v>0.216054</v>
       </c>
     </row>
     <row r="49">
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0456</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.0228</v>
       </c>
       <c r="M124" s="1" t="inlineStr">
         <is>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010068</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.10106</v>
       </c>
     </row>
     <row r="125">
@@ -7281,10 +7281,10 @@
         </is>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0456</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.0228</v>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
@@ -7292,10 +7292,10 @@
         </is>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010068</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.10106</v>
       </c>
     </row>
     <row r="126">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13684,7 +13684,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -23852,7 +23852,11 @@
           <t>Lease payments 7</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -28078,7 +28082,11 @@
           <t>Lease payments (Note 6)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VRTS.xlsx
+++ b/output/pdf_financials_xlsx/VRTS.xlsx
@@ -1259,7 +1259,7 @@
         <v>0.020915</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.014821</v>
+        <v>0.010291</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -2095,7 +2095,7 @@
         <v>-46.64258156597757</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-3.084347679507537</v>
+        <v>-2.141624854585524</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -6426,13 +6426,13 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002711</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.079233</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003142</v>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
@@ -7809,13 +7809,13 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002711</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.079233</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003142</v>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.424824</v>
+        <v>-0.504057</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
@@ -31636,7 +31636,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>
@@ -44126,7 +44130,11 @@
           <t>INCOME TAX RECOVERY (Note 11)</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -47692,7 +47700,11 @@
           <t>Income Tax Recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
